--- a/core/utils/docs_proj_p/distgradeunificada9.xlsx
+++ b/core/utils/docs_proj_p/distgradeunificada9.xlsx
@@ -21715,7 +21715,9 @@
       <c r="G662" s="9"/>
       <c r="H662" s="9"/>
       <c r="I662" s="9"/>
-      <c r="J662" s="9"/>
+      <c r="J662" s="9" t="n">
+        <v>9</v>
+      </c>
       <c r="K662" s="9"/>
       <c r="L662" s="9"/>
       <c r="M662" s="9"/>
@@ -21747,7 +21749,9 @@
       <c r="G663" s="9"/>
       <c r="H663" s="9"/>
       <c r="I663" s="9"/>
-      <c r="J663" s="9"/>
+      <c r="J663" s="9" t="n">
+        <v>9</v>
+      </c>
       <c r="K663" s="9"/>
       <c r="L663" s="9"/>
       <c r="M663" s="9"/>
@@ -21843,10 +21847,14 @@
       <c r="G666" s="9"/>
       <c r="H666" s="9"/>
       <c r="I666" s="9"/>
-      <c r="J666" s="9"/>
+      <c r="J666" s="9" t="n">
+        <v>9</v>
+      </c>
       <c r="K666" s="9"/>
       <c r="L666" s="9"/>
-      <c r="M666" s="9"/>
+      <c r="M666" s="9" t="n">
+        <v>9</v>
+      </c>
       <c r="N666" s="9"/>
       <c r="O666" s="9"/>
       <c r="P666" s="9"/>
@@ -21907,10 +21915,14 @@
       <c r="G668" s="9"/>
       <c r="H668" s="9"/>
       <c r="I668" s="9"/>
-      <c r="J668" s="9"/>
+      <c r="J668" s="9" t="n">
+        <v>9</v>
+      </c>
       <c r="K668" s="9"/>
       <c r="L668" s="9"/>
-      <c r="M668" s="9"/>
+      <c r="M668" s="9" t="n">
+        <v>9</v>
+      </c>
       <c r="N668" s="9"/>
       <c r="O668" s="9"/>
       <c r="P668" s="9"/>
@@ -21940,7 +21952,9 @@
       <c r="H669" s="9"/>
       <c r="I669" s="9"/>
       <c r="J669" s="9"/>
-      <c r="K669" s="9"/>
+      <c r="K669" s="9" t="n">
+        <v>9</v>
+      </c>
       <c r="L669" s="9"/>
       <c r="M669" s="9"/>
       <c r="N669" s="9"/>
@@ -21972,9 +21986,13 @@
       <c r="H670" s="9"/>
       <c r="I670" s="9"/>
       <c r="J670" s="9"/>
-      <c r="K670" s="9"/>
+      <c r="K670" s="9" t="n">
+        <v>9</v>
+      </c>
       <c r="L670" s="9"/>
-      <c r="M670" s="9"/>
+      <c r="M670" s="9" t="n">
+        <v>9</v>
+      </c>
       <c r="N670" s="9"/>
       <c r="O670" s="9"/>
       <c r="P670" s="9"/>
@@ -22004,7 +22022,9 @@
       <c r="H671" s="9"/>
       <c r="I671" s="9"/>
       <c r="J671" s="9"/>
-      <c r="K671" s="9"/>
+      <c r="K671" s="9" t="n">
+        <v>9</v>
+      </c>
       <c r="L671" s="9"/>
       <c r="M671" s="9"/>
       <c r="N671" s="9"/>
@@ -22036,7 +22056,9 @@
       <c r="H672" s="9"/>
       <c r="I672" s="9"/>
       <c r="J672" s="9"/>
-      <c r="K672" s="9"/>
+      <c r="K672" s="9" t="n">
+        <v>9</v>
+      </c>
       <c r="L672" s="9"/>
       <c r="M672" s="9"/>
       <c r="N672" s="9"/>
@@ -22067,7 +22089,9 @@
       <c r="G673" s="9"/>
       <c r="H673" s="9"/>
       <c r="I673" s="9"/>
-      <c r="J673" s="9"/>
+      <c r="J673" s="9" t="n">
+        <v>9</v>
+      </c>
       <c r="K673" s="9"/>
       <c r="L673" s="9"/>
       <c r="M673" s="9"/>
@@ -22096,7 +22120,9 @@
       <c r="F674" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="G674" s="9"/>
+      <c r="G674" s="9" t="n">
+        <v>9</v>
+      </c>
       <c r="H674" s="9"/>
       <c r="I674" s="9"/>
       <c r="J674" s="9"/>
@@ -22194,7 +22220,9 @@
       </c>
       <c r="G677" s="9"/>
       <c r="H677" s="9"/>
-      <c r="I677" s="9"/>
+      <c r="I677" s="9" t="n">
+        <v>9</v>
+      </c>
       <c r="J677" s="9"/>
       <c r="K677" s="9"/>
       <c r="L677" s="9"/>
@@ -22228,7 +22256,9 @@
       <c r="H678" s="9"/>
       <c r="I678" s="9"/>
       <c r="J678" s="9"/>
-      <c r="K678" s="9"/>
+      <c r="K678" s="9" t="n">
+        <v>9</v>
+      </c>
       <c r="L678" s="9"/>
       <c r="M678" s="9"/>
       <c r="N678" s="9"/>
@@ -22292,7 +22322,9 @@
       <c r="H680" s="9"/>
       <c r="I680" s="9"/>
       <c r="J680" s="9"/>
-      <c r="K680" s="9"/>
+      <c r="K680" s="9" t="n">
+        <v>9</v>
+      </c>
       <c r="L680" s="9"/>
       <c r="M680" s="9"/>
       <c r="N680" s="9"/>
@@ -22352,11 +22384,21 @@
       <c r="F682" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="G682" s="9"/>
-      <c r="H682" s="9"/>
-      <c r="I682" s="9"/>
-      <c r="J682" s="9"/>
-      <c r="K682" s="9"/>
+      <c r="G682" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="H682" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="I682" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="J682" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="K682" s="9" t="n">
+        <v>9</v>
+      </c>
       <c r="L682" s="9"/>
       <c r="M682" s="9"/>
       <c r="N682" s="9"/>
